--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_4.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01755530496562387</v>
+        <v>0.01136894964979167</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008411541098893133</v>
+        <v>0.00840949336849749</v>
       </c>
       <c r="C2" t="n">
-        <v>25452324</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25452324</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>18412146</v>
+        <v>4502563</v>
       </c>
       <c r="L2" t="n">
-        <v>10645943</v>
+        <v>2531638</v>
       </c>
       <c r="M2" t="n">
-        <v>2677904</v>
+        <v>611289</v>
       </c>
       <c r="N2" t="n">
-        <v>145571</v>
+        <v>29497</v>
       </c>
       <c r="O2" t="n">
-        <v>1612451</v>
+        <v>379589</v>
       </c>
       <c r="P2" t="n">
-        <v>649769</v>
+        <v>154099</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999884366989136</v>
+        <v>0.9999774694442749</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9026709794998169</v>
+        <v>0.8809610605239868</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8007271885871887</v>
+        <v>0.7615930438041687</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7406709790229797</v>
+        <v>0.7031766176223755</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5218945145606995</v>
+        <v>0.394102543592453</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7929019927978516</v>
+        <v>0.7540384531021118</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8511659502983093</v>
+        <v>0.8249588012695312</v>
       </c>
       <c r="X2" t="n">
-        <v>25452324</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25452324</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19453918</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11974836</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3208013</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236747</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1837712</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720176</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565864205360413</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113011956214905</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579807281494141</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6621256470680237</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019365906715393</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.93143230676651</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.004243965731796175</v>
+        <v>0.002674272499452904</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002015256325970591</v>
+        <v>0.002015272774735009</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>18412146</v>
+        <v>4502563</v>
       </c>
       <c r="E3" t="n">
-        <v>1851610</v>
+        <v>546649</v>
       </c>
       <c r="F3" t="n">
-        <v>41347</v>
+        <v>7407</v>
       </c>
       <c r="G3" t="n">
-        <v>7632</v>
+        <v>1132</v>
       </c>
       <c r="H3" t="n">
-        <v>1876</v>
+        <v>447</v>
       </c>
       <c r="I3" t="n">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="J3" t="n">
-        <v>40384182</v>
+        <v>10069477</v>
       </c>
       <c r="K3" t="n">
-        <v>43536760</v>
+        <v>10749336</v>
       </c>
       <c r="L3" t="n">
-        <v>50028253</v>
+        <v>12338967</v>
       </c>
       <c r="M3" t="n">
-        <v>61158034</v>
+        <v>15223444</v>
       </c>
       <c r="N3" t="n">
-        <v>65345663</v>
+        <v>16281278</v>
       </c>
       <c r="O3" t="n">
-        <v>63377356</v>
+        <v>15782596</v>
       </c>
       <c r="P3" t="n">
-        <v>64949860</v>
+        <v>16189957</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9063423871994019</v>
+        <v>0.8901406526565552</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8090146780014038</v>
+        <v>0.7707749009132385</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7157952785491943</v>
+        <v>0.6541208028793335</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4068729281425476</v>
+        <v>0.330043762922287</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7910810708999634</v>
+        <v>0.7448983192443848</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8402308225631714</v>
+        <v>0.7970115542411804</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19453918</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>798777</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34422</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27363</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40384476</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44639126</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51512118</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61564627</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65358211</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63598706</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>65010462</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576238393783569</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100009202957153</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574917316436768</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6617110967636108</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015958309173584</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312757253646851</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04950866693283029</v>
+        <v>0.03509917791432888</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03184854034087193</v>
+        <v>0.031840082348875</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1881271</v>
+        <v>577071</v>
       </c>
       <c r="E4" t="n">
-        <v>10645943</v>
+        <v>2531638</v>
       </c>
       <c r="F4" t="n">
-        <v>570885</v>
+        <v>157455</v>
       </c>
       <c r="G4" t="n">
-        <v>18398</v>
+        <v>5702</v>
       </c>
       <c r="H4" t="n">
-        <v>39344</v>
+        <v>11752</v>
       </c>
       <c r="I4" t="n">
-        <v>3296</v>
+        <v>915</v>
       </c>
       <c r="J4" t="n">
-        <v>294</v>
+        <v>143</v>
       </c>
       <c r="K4" t="n">
-        <v>1985260</v>
+        <v>608404</v>
       </c>
       <c r="L4" t="n">
-        <v>2649400</v>
+        <v>792497</v>
       </c>
       <c r="M4" t="n">
-        <v>937607</v>
+        <v>258036</v>
       </c>
       <c r="N4" t="n">
-        <v>133357</v>
+        <v>45349</v>
       </c>
       <c r="O4" t="n">
-        <v>421156</v>
+        <v>123819</v>
       </c>
       <c r="P4" t="n">
-        <v>113618</v>
+        <v>32697</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999942183494568</v>
+        <v>0.9999887347221375</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9045029282569885</v>
+        <v>0.8855270743370056</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8048495650291443</v>
+        <v>0.7661564946174622</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7280207276344299</v>
+        <v>0.6777622103691101</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4572614133358002</v>
+        <v>0.3592398166656494</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7919905185699463</v>
+        <v>0.7494405508041382</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8456630706787109</v>
+        <v>0.8107444047927856</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>824373</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11974836</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332978</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22096</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4592</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>882894</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1165535</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>531014</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120809</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199806</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571048021316528</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106505513191223</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577361702919006</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619182825088501</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017662405967712</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313539862632751</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>63881</v>
+        <v>19588</v>
       </c>
       <c r="E5" t="n">
-        <v>696591</v>
+        <v>214010</v>
       </c>
       <c r="F5" t="n">
-        <v>2677904</v>
+        <v>611289</v>
       </c>
       <c r="G5" t="n">
-        <v>56619</v>
+        <v>19200</v>
       </c>
       <c r="H5" t="n">
-        <v>230168</v>
+        <v>65578</v>
       </c>
       <c r="I5" t="n">
-        <v>15976</v>
+        <v>4846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1902634</v>
+        <v>555697</v>
       </c>
       <c r="L5" t="n">
-        <v>2513204</v>
+        <v>752898</v>
       </c>
       <c r="M5" t="n">
-        <v>1063255</v>
+        <v>323231</v>
       </c>
       <c r="N5" t="n">
-        <v>212209</v>
+        <v>59876</v>
       </c>
       <c r="O5" t="n">
-        <v>425837</v>
+        <v>129996</v>
       </c>
       <c r="P5" t="n">
-        <v>123553</v>
+        <v>39247</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999955296516418</v>
+        <v>0.9999912977218628</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9409465193748474</v>
+        <v>0.9290874004364014</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9215848445892334</v>
+        <v>0.905860424041748</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9696087837219238</v>
+        <v>0.9645914435386658</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9947511553764343</v>
+        <v>0.9935901165008545</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9871349334716797</v>
+        <v>0.9845385551452637</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9963976144790649</v>
+        <v>0.9956174492835999</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32300</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>341661</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3208013</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39915</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116738</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>860862</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1184311</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>533146</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>121033</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200576</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53146</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735139608383179</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643080234527588</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838364124298096</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939185976982117</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983875155448914</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>39664</v>
+        <v>11704</v>
       </c>
       <c r="E6" t="n">
-        <v>57938</v>
+        <v>18279</v>
       </c>
       <c r="F6" t="n">
-        <v>71201</v>
+        <v>17990</v>
       </c>
       <c r="G6" t="n">
-        <v>145571</v>
+        <v>29497</v>
       </c>
       <c r="H6" t="n">
-        <v>39372</v>
+        <v>10778</v>
       </c>
       <c r="I6" t="n">
-        <v>3985</v>
+        <v>1114</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25997</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21526</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43617</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236747</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27969</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D7" t="n">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>41159</v>
+        <v>12954</v>
       </c>
       <c r="F7" t="n">
-        <v>246019</v>
+        <v>72733</v>
       </c>
       <c r="G7" t="n">
-        <v>47985</v>
+        <v>18457</v>
       </c>
       <c r="H7" t="n">
-        <v>1612451</v>
+        <v>379589</v>
       </c>
       <c r="I7" t="n">
-        <v>90200</v>
+        <v>25761</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3247</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118676</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30373</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1837712</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>2102</v>
+        <v>605</v>
       </c>
       <c r="F8" t="n">
-        <v>8155</v>
+        <v>2451</v>
       </c>
       <c r="G8" t="n">
-        <v>2723</v>
+        <v>858</v>
       </c>
       <c r="H8" t="n">
-        <v>110396</v>
+        <v>35264</v>
       </c>
       <c r="I8" t="n">
-        <v>649769</v>
+        <v>154099</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1321</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1062</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50327</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720176</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
